--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/12 (수)</t>
+          <t>08/15 (토)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/13 (목)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/14 (금)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/15 (토)</t>
+          <t>08/16 (일)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/16 (일)</t>
+          <t>08/17 (월)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/17 (월)</t>
+          <t>08/18 (화)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/19 (수)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/20 (목)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/21 (금)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46282</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/18 (화)</t>
+          <t>08/22 (토)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/19 (수)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/20 (목)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/21 (금)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/22 (토)</t>
+          <t>08/23 (일)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/24 (월)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/25 (화)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/26 (수)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>08/27 (목)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>08/28 (금)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46287</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/23 (일)</t>
+          <t>08/29 (토)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/24 (월)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/25 (화)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>08/26 (수)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>08/27 (목)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>08/28 (금)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/29 (토)</t>
+          <t>08/30 (일)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/30 (일)</t>
+          <t>08/31 (월)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>08/31 (월)</t>
+          <t>09/01 (화)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/01 (화)</t>
+          <t>09/02 (수)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/03 (목)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/04 (금)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
@@ -19804,7 +19804,7 @@
     <row r="88">
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
@@ -19828,7 +19828,7 @@
     <row r="89">
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
@@ -19852,7 +19852,7 @@
     <row r="90">
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C90" s="32" t="inlineStr">
@@ -19876,7 +19876,7 @@
     <row r="91">
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C91" s="32" t="inlineStr">
@@ -19900,7 +19900,7 @@
     <row r="92">
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C92" s="32" t="inlineStr">
@@ -19924,7 +19924,7 @@
     <row r="93">
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
@@ -19948,7 +19948,7 @@
     <row r="94">
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
@@ -19972,7 +19972,7 @@
     <row r="95">
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C95" s="32" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="96">
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C96" s="32" t="inlineStr">
@@ -20020,7 +20020,7 @@
     <row r="97">
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
@@ -20044,7 +20044,7 @@
     <row r="98">
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
@@ -20068,7 +20068,7 @@
     <row r="99">
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C99" s="32" t="inlineStr">
@@ -20092,7 +20092,7 @@
     <row r="100">
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C100" s="32" t="inlineStr">
@@ -20116,7 +20116,7 @@
     <row r="101">
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
@@ -20140,7 +20140,7 @@
     <row r="102">
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
@@ -20164,7 +20164,7 @@
     <row r="103">
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C103" s="32" t="inlineStr">
@@ -20188,7 +20188,7 @@
     <row r="104">
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/05 (토)</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
@@ -20212,7 +20212,7 @@
     <row r="105">
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -20236,7 +20236,7 @@
     <row r="106">
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C106" s="32" t="inlineStr">
@@ -20260,7 +20260,7 @@
     <row r="107">
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C107" s="32" t="inlineStr">
@@ -20284,7 +20284,7 @@
     <row r="108">
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
@@ -20308,7 +20308,7 @@
     <row r="109">
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
@@ -20332,7 +20332,7 @@
     <row r="110">
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
@@ -20356,7 +20356,7 @@
     <row r="111">
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
@@ -20380,7 +20380,7 @@
     <row r="112">
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
@@ -20404,7 +20404,7 @@
     <row r="113">
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C113" s="32" t="inlineStr">
@@ -20428,7 +20428,7 @@
     <row r="114">
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C114" s="32" t="inlineStr">
@@ -20452,7 +20452,7 @@
     <row r="115">
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
@@ -20476,7 +20476,7 @@
     <row r="116">
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
@@ -20500,7 +20500,7 @@
     <row r="117">
       <c r="B117" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
@@ -20524,7 +20524,7 @@
     <row r="118">
       <c r="B118" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
@@ -20548,7 +20548,7 @@
     <row r="119">
       <c r="B119" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
@@ -20572,7 +20572,7 @@
     <row r="120">
       <c r="B120" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
@@ -20596,7 +20596,7 @@
     <row r="121">
       <c r="B121" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C121" s="32" t="inlineStr">
@@ -20620,7 +20620,7 @@
     <row r="122">
       <c r="B122" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
@@ -20644,7 +20644,7 @@
     <row r="123">
       <c r="B123" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C123" s="32" t="inlineStr">
@@ -20668,7 +20668,7 @@
     <row r="124">
       <c r="B124" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C124" s="32" t="inlineStr">
@@ -20692,7 +20692,7 @@
     <row r="125">
       <c r="B125" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C125" s="32" t="inlineStr">
@@ -20716,7 +20716,7 @@
     <row r="126">
       <c r="B126" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C126" s="32" t="inlineStr">
@@ -20740,7 +20740,7 @@
     <row r="127">
       <c r="B127" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
@@ -20764,7 +20764,7 @@
     <row r="128">
       <c r="B128" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
@@ -20788,7 +20788,7 @@
     <row r="129">
       <c r="B129" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
@@ -20812,7 +20812,7 @@
     <row r="130">
       <c r="B130" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C130" s="32" t="inlineStr">
@@ -20836,7 +20836,7 @@
     <row r="131">
       <c r="B131" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
@@ -20860,7 +20860,7 @@
     <row r="132">
       <c r="B132" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
@@ -20884,7 +20884,7 @@
     <row r="133">
       <c r="B133" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
@@ -20908,7 +20908,7 @@
     <row r="134">
       <c r="B134" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
@@ -20932,7 +20932,7 @@
     <row r="135">
       <c r="B135" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
@@ -20956,7 +20956,7 @@
     <row r="136">
       <c r="B136" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
@@ -20980,7 +20980,7 @@
     <row r="137">
       <c r="B137" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C137" s="32" t="inlineStr">
@@ -21004,7 +21004,7 @@
     <row r="138">
       <c r="B138" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
@@ -21028,7 +21028,7 @@
     <row r="139">
       <c r="B139" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
@@ -21052,7 +21052,7 @@
     <row r="140">
       <c r="B140" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
@@ -21076,7 +21076,7 @@
     <row r="141">
       <c r="B141" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C141" s="32" t="inlineStr">
@@ -21100,7 +21100,7 @@
     <row r="142">
       <c r="B142" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C142" s="32" t="inlineStr">
@@ -21124,7 +21124,7 @@
     <row r="143">
       <c r="B143" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
@@ -21148,7 +21148,7 @@
     <row r="144">
       <c r="B144" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
@@ -21172,7 +21172,7 @@
     <row r="145">
       <c r="B145" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
@@ -21196,7 +21196,7 @@
     <row r="146">
       <c r="B146" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
@@ -21220,7 +21220,7 @@
     <row r="147">
       <c r="B147" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
@@ -21244,7 +21244,7 @@
     <row r="148">
       <c r="B148" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
@@ -21268,7 +21268,7 @@
     <row r="149">
       <c r="B149" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C149" s="32" t="inlineStr">
@@ -21292,7 +21292,7 @@
     <row r="150">
       <c r="B150" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C150" s="32" t="inlineStr">
@@ -21316,7 +21316,7 @@
     <row r="151">
       <c r="B151" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C151" s="32" t="inlineStr">
@@ -21340,7 +21340,7 @@
     <row r="152">
       <c r="B152" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C152" s="32" t="inlineStr">
@@ -21364,7 +21364,7 @@
     <row r="153">
       <c r="B153" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C153" s="32" t="inlineStr">
@@ -21388,7 +21388,7 @@
     <row r="154">
       <c r="B154" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C154" s="32" t="inlineStr">
@@ -21412,7 +21412,7 @@
     <row r="155">
       <c r="B155" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C155" s="32" t="inlineStr">
@@ -21436,7 +21436,7 @@
     <row r="156">
       <c r="B156" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C156" s="32" t="inlineStr">
@@ -21460,7 +21460,7 @@
     <row r="157">
       <c r="B157" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C157" s="32" t="inlineStr">
@@ -21484,7 +21484,7 @@
     <row r="158">
       <c r="B158" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C158" s="32" t="inlineStr">
@@ -21508,7 +21508,7 @@
     <row r="159">
       <c r="B159" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C159" s="32" t="inlineStr">
@@ -21532,7 +21532,7 @@
     <row r="160">
       <c r="B160" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C160" s="32" t="inlineStr">
@@ -21556,7 +21556,7 @@
     <row r="161">
       <c r="B161" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C161" s="32" t="inlineStr">
@@ -21580,7 +21580,7 @@
     <row r="162">
       <c r="B162" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C162" s="32" t="inlineStr">
@@ -21604,7 +21604,7 @@
     <row r="163">
       <c r="B163" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C163" s="32" t="inlineStr">
@@ -21628,7 +21628,7 @@
     <row r="164">
       <c r="B164" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C164" s="32" t="inlineStr">
@@ -21652,7 +21652,7 @@
     <row r="165">
       <c r="B165" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C165" s="32" t="inlineStr">
@@ -21676,7 +21676,7 @@
     <row r="166">
       <c r="B166" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C166" s="32" t="inlineStr">
@@ -21700,7 +21700,7 @@
     <row r="167">
       <c r="B167" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C167" s="32" t="inlineStr">
@@ -21724,7 +21724,7 @@
     <row r="168">
       <c r="B168" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C168" s="32" t="inlineStr">
@@ -21748,7 +21748,7 @@
     <row r="169">
       <c r="B169" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C169" s="32" t="inlineStr">
@@ -21772,7 +21772,7 @@
     <row r="170">
       <c r="B170" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C170" s="32" t="inlineStr">
@@ -21796,7 +21796,7 @@
     <row r="171">
       <c r="B171" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C171" s="32" t="inlineStr">
@@ -21820,7 +21820,7 @@
     <row r="172">
       <c r="B172" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C172" s="32" t="inlineStr">
@@ -21844,7 +21844,7 @@
     <row r="173">
       <c r="B173" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C173" s="32" t="inlineStr">
@@ -21868,7 +21868,7 @@
     <row r="174">
       <c r="B174" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C174" s="32" t="inlineStr">
@@ -21892,7 +21892,7 @@
     <row r="175">
       <c r="B175" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C175" s="32" t="inlineStr">
@@ -21916,7 +21916,7 @@
     <row r="176">
       <c r="B176" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C176" s="32" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <row r="177">
       <c r="B177" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C177" s="32" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="178">
       <c r="B178" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C178" s="32" t="inlineStr">
@@ -21988,7 +21988,7 @@
     <row r="179">
       <c r="B179" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C179" s="32" t="inlineStr">
@@ -22012,7 +22012,7 @@
     <row r="180">
       <c r="B180" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C180" s="32" t="inlineStr">
@@ -22036,7 +22036,7 @@
     <row r="181">
       <c r="B181" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C181" s="32" t="inlineStr">
@@ -22060,7 +22060,7 @@
     <row r="182">
       <c r="B182" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C182" s="32" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="183">
       <c r="B183" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C183" s="32" t="inlineStr">
@@ -22108,7 +22108,7 @@
     <row r="184">
       <c r="B184" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C184" s="32" t="inlineStr">
@@ -22132,7 +22132,7 @@
     <row r="185">
       <c r="B185" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C185" s="32" t="inlineStr">
@@ -22156,7 +22156,7 @@
     <row r="186">
       <c r="B186" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C186" s="32" t="inlineStr">
@@ -22180,7 +22180,7 @@
     <row r="187">
       <c r="B187" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C187" s="32" t="inlineStr">
@@ -22204,7 +22204,7 @@
     <row r="188">
       <c r="B188" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C188" s="32" t="inlineStr">
@@ -22228,7 +22228,7 @@
     <row r="189">
       <c r="B189" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C189" s="32" t="inlineStr">
@@ -22252,7 +22252,7 @@
     <row r="190">
       <c r="B190" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C190" s="32" t="inlineStr">
@@ -22276,7 +22276,7 @@
     <row r="191">
       <c r="B191" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C191" s="32" t="inlineStr">
@@ -22300,7 +22300,7 @@
     <row r="192">
       <c r="B192" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C192" s="32" t="inlineStr">
@@ -22324,7 +22324,7 @@
     <row r="193">
       <c r="B193" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C193" s="32" t="inlineStr">
@@ -22348,7 +22348,7 @@
     <row r="194">
       <c r="B194" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C194" s="32" t="inlineStr">
@@ -22372,7 +22372,7 @@
     <row r="195">
       <c r="B195" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C195" s="32" t="inlineStr">
@@ -22396,7 +22396,7 @@
     <row r="196">
       <c r="B196" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C196" s="32" t="inlineStr">
@@ -22420,7 +22420,7 @@
     <row r="197">
       <c r="B197" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C197" s="32" t="inlineStr">
@@ -22444,7 +22444,7 @@
     <row r="198">
       <c r="B198" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C198" s="32" t="inlineStr">
@@ -22468,7 +22468,7 @@
     <row r="199">
       <c r="B199" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C199" s="32" t="inlineStr">
@@ -22492,7 +22492,7 @@
     <row r="200">
       <c r="B200" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C200" s="32" t="inlineStr">
@@ -22516,7 +22516,7 @@
     <row r="201">
       <c r="B201" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C201" s="32" t="inlineStr">
@@ -22540,7 +22540,7 @@
     <row r="202">
       <c r="B202" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C202" s="32" t="inlineStr">
@@ -22564,7 +22564,7 @@
     <row r="203">
       <c r="B203" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C203" s="32" t="inlineStr">
@@ -22588,7 +22588,7 @@
     <row r="204">
       <c r="B204" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C204" s="32" t="inlineStr">
@@ -22612,7 +22612,7 @@
     <row r="205">
       <c r="B205" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C205" s="32" t="inlineStr">
@@ -22636,7 +22636,7 @@
     <row r="206">
       <c r="B206" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C206" s="32" t="inlineStr">
@@ -22660,7 +22660,7 @@
     <row r="207">
       <c r="B207" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C207" s="32" t="inlineStr">
@@ -22684,7 +22684,7 @@
     <row r="208">
       <c r="B208" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C208" s="32" t="inlineStr">
@@ -22708,7 +22708,7 @@
     <row r="209">
       <c r="B209" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C209" s="32" t="inlineStr">
@@ -22732,7 +22732,7 @@
     <row r="210">
       <c r="B210" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C210" s="32" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="211">
       <c r="B211" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C211" s="32" t="inlineStr">
@@ -22780,7 +22780,7 @@
     <row r="212">
       <c r="B212" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C212" s="32" t="inlineStr">
@@ -22804,7 +22804,7 @@
     <row r="213">
       <c r="B213" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C213" s="32" t="inlineStr">
@@ -22828,7 +22828,7 @@
     <row r="214">
       <c r="B214" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C214" s="32" t="inlineStr">
@@ -22852,7 +22852,7 @@
     <row r="215">
       <c r="B215" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C215" s="32" t="inlineStr">
@@ -22876,7 +22876,7 @@
     <row r="216">
       <c r="B216" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C216" s="32" t="inlineStr">
@@ -22900,7 +22900,7 @@
     <row r="217">
       <c r="B217" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C217" s="32" t="inlineStr">
@@ -22924,7 +22924,7 @@
     <row r="218">
       <c r="B218" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C218" s="32" t="inlineStr">
@@ -22948,7 +22948,7 @@
     <row r="219">
       <c r="B219" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C219" s="32" t="inlineStr">
@@ -22972,7 +22972,7 @@
     <row r="220">
       <c r="B220" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C220" s="32" t="inlineStr">
@@ -22996,7 +22996,7 @@
     <row r="221">
       <c r="B221" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C221" s="32" t="inlineStr">
@@ -23020,7 +23020,7 @@
     <row r="222">
       <c r="B222" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C222" s="32" t="inlineStr">
@@ -23044,7 +23044,7 @@
     <row r="223">
       <c r="B223" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C223" s="32" t="inlineStr">
@@ -23068,7 +23068,7 @@
     <row r="224">
       <c r="B224" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C224" s="32" t="inlineStr">
@@ -23092,7 +23092,7 @@
     <row r="225">
       <c r="B225" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C225" s="32" t="inlineStr">
@@ -23116,7 +23116,7 @@
     <row r="226">
       <c r="B226" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C226" s="32" t="inlineStr">
@@ -23140,7 +23140,7 @@
     <row r="227">
       <c r="B227" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C227" s="32" t="inlineStr">
@@ -23164,7 +23164,7 @@
     <row r="228">
       <c r="B228" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C228" s="32" t="inlineStr">
@@ -23188,7 +23188,7 @@
     <row r="229">
       <c r="B229" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C229" s="32" t="inlineStr">
@@ -23212,7 +23212,7 @@
     <row r="230">
       <c r="B230" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C230" s="32" t="inlineStr">
@@ -23236,7 +23236,7 @@
     <row r="231">
       <c r="B231" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C231" s="32" t="inlineStr">
@@ -23260,7 +23260,7 @@
     <row r="232">
       <c r="B232" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C232" s="32" t="inlineStr">
@@ -23284,7 +23284,7 @@
     <row r="233">
       <c r="B233" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C233" s="32" t="inlineStr">
@@ -23308,7 +23308,7 @@
     <row r="234">
       <c r="B234" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C234" s="32" t="inlineStr">
@@ -23332,7 +23332,7 @@
     <row r="235">
       <c r="B235" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C235" s="32" t="inlineStr">
@@ -23356,7 +23356,7 @@
     <row r="236">
       <c r="B236" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C236" s="32" t="inlineStr">
@@ -23380,7 +23380,7 @@
     <row r="237">
       <c r="B237" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C237" s="32" t="inlineStr">
@@ -23404,7 +23404,7 @@
     <row r="238">
       <c r="B238" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C238" s="32" t="inlineStr">
@@ -23428,7 +23428,7 @@
     <row r="239">
       <c r="B239" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C239" s="32" t="inlineStr">
@@ -23452,7 +23452,7 @@
     <row r="240">
       <c r="B240" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C240" s="32" t="inlineStr">
@@ -23476,7 +23476,7 @@
     <row r="241">
       <c r="B241" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C241" s="32" t="inlineStr">
@@ -23500,7 +23500,7 @@
     <row r="242">
       <c r="B242" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C242" s="32" t="inlineStr">
@@ -23524,7 +23524,7 @@
     <row r="243">
       <c r="B243" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C243" s="32" t="inlineStr">
@@ -23548,7 +23548,7 @@
     <row r="244">
       <c r="B244" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C244" s="32" t="inlineStr">
@@ -23572,7 +23572,7 @@
     <row r="245">
       <c r="B245" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C245" s="32" t="inlineStr">
@@ -23596,7 +23596,7 @@
     <row r="246">
       <c r="B246" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C246" s="32" t="inlineStr">
@@ -23620,7 +23620,7 @@
     <row r="247">
       <c r="B247" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C247" s="32" t="inlineStr">
@@ -23644,7 +23644,7 @@
     <row r="248">
       <c r="B248" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C248" s="32" t="inlineStr">
@@ -23668,7 +23668,7 @@
     <row r="249">
       <c r="B249" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C249" s="32" t="inlineStr">
@@ -23692,7 +23692,7 @@
     <row r="250">
       <c r="B250" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C250" s="32" t="inlineStr">
@@ -23716,7 +23716,7 @@
     <row r="251">
       <c r="B251" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C251" s="32" t="inlineStr">
@@ -23740,7 +23740,7 @@
     <row r="252">
       <c r="B252" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C252" s="32" t="inlineStr">
@@ -23764,7 +23764,7 @@
     <row r="253">
       <c r="B253" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C253" s="32" t="inlineStr">
@@ -23788,7 +23788,7 @@
     <row r="254">
       <c r="B254" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C254" s="32" t="inlineStr">
@@ -23812,7 +23812,7 @@
     <row r="255">
       <c r="B255" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C255" s="32" t="inlineStr">
@@ -23836,7 +23836,7 @@
     <row r="256">
       <c r="B256" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C256" s="32" t="inlineStr">
@@ -23860,7 +23860,7 @@
     <row r="257">
       <c r="B257" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C257" s="32" t="inlineStr">
@@ -23884,7 +23884,7 @@
     <row r="258">
       <c r="B258" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C258" s="32" t="inlineStr">
@@ -23908,7 +23908,7 @@
     <row r="259">
       <c r="B259" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C259" s="32" t="inlineStr">
@@ -23932,7 +23932,7 @@
     <row r="260">
       <c r="B260" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C260" s="32" t="inlineStr">
@@ -23956,7 +23956,7 @@
     <row r="261">
       <c r="B261" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C261" s="32" t="inlineStr">
@@ -23980,7 +23980,7 @@
     <row r="262">
       <c r="B262" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C262" s="32" t="inlineStr">
@@ -24004,7 +24004,7 @@
     <row r="263">
       <c r="B263" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C263" s="32" t="inlineStr">
@@ -24028,7 +24028,7 @@
     <row r="264">
       <c r="B264" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C264" s="32" t="inlineStr">
@@ -24052,7 +24052,7 @@
     <row r="265">
       <c r="B265" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C265" s="32" t="inlineStr">
@@ -24076,7 +24076,7 @@
     <row r="266">
       <c r="B266" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C266" s="32" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="267">
       <c r="B267" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C267" s="32" t="inlineStr">
@@ -24124,7 +24124,7 @@
     <row r="268">
       <c r="B268" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C268" s="32" t="inlineStr">
@@ -24148,7 +24148,7 @@
     <row r="269">
       <c r="B269" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C269" s="32" t="inlineStr">
@@ -24172,7 +24172,7 @@
     <row r="270">
       <c r="B270" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C270" s="32" t="inlineStr">
@@ -24196,7 +24196,7 @@
     <row r="271">
       <c r="B271" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C271" s="32" t="inlineStr">
@@ -24220,7 +24220,7 @@
     <row r="272">
       <c r="B272" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C272" s="32" t="inlineStr">
@@ -24244,7 +24244,7 @@
     <row r="273">
       <c r="B273" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C273" s="32" t="inlineStr">
@@ -24268,7 +24268,7 @@
     <row r="274">
       <c r="B274" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C274" s="32" t="inlineStr">
@@ -24292,7 +24292,7 @@
     <row r="275">
       <c r="B275" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C275" s="32" t="inlineStr">
@@ -24316,7 +24316,7 @@
     <row r="276">
       <c r="B276" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C276" s="32" t="inlineStr">
@@ -24340,7 +24340,7 @@
     <row r="277">
       <c r="B277" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C277" s="32" t="inlineStr">
@@ -24364,7 +24364,7 @@
     <row r="278">
       <c r="B278" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C278" s="32" t="inlineStr">
@@ -24388,7 +24388,7 @@
     <row r="279">
       <c r="B279" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C279" s="32" t="inlineStr">
@@ -24412,7 +24412,7 @@
     <row r="280">
       <c r="B280" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C280" s="32" t="inlineStr">
@@ -24436,7 +24436,7 @@
     <row r="281">
       <c r="B281" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C281" s="32" t="inlineStr">
@@ -24460,7 +24460,7 @@
     <row r="282">
       <c r="B282" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C282" s="32" t="inlineStr">
@@ -24484,7 +24484,7 @@
     <row r="283">
       <c r="B283" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C283" s="32" t="inlineStr">
@@ -24508,7 +24508,7 @@
     <row r="284">
       <c r="B284" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C284" s="32" t="inlineStr">
@@ -24532,7 +24532,7 @@
     <row r="285">
       <c r="B285" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C285" s="32" t="inlineStr">
@@ -24556,7 +24556,7 @@
     <row r="286">
       <c r="B286" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C286" s="32" t="inlineStr">
@@ -24580,7 +24580,7 @@
     <row r="287">
       <c r="B287" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C287" s="32" t="inlineStr">
@@ -24604,7 +24604,7 @@
     <row r="288">
       <c r="B288" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C288" s="32" t="inlineStr">
@@ -24628,7 +24628,7 @@
     <row r="289">
       <c r="B289" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C289" s="32" t="inlineStr">
@@ -24652,7 +24652,7 @@
     <row r="290">
       <c r="B290" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C290" s="32" t="inlineStr">
@@ -24676,7 +24676,7 @@
     <row r="291">
       <c r="B291" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C291" s="32" t="inlineStr">
@@ -24700,7 +24700,7 @@
     <row r="292">
       <c r="B292" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C292" s="32" t="inlineStr">
@@ -24724,7 +24724,7 @@
     <row r="293">
       <c r="B293" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C293" s="32" t="inlineStr">
@@ -24748,7 +24748,7 @@
     <row r="294">
       <c r="B294" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C294" s="32" t="inlineStr">
@@ -24772,7 +24772,7 @@
     <row r="295">
       <c r="B295" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C295" s="32" t="inlineStr">
@@ -24796,7 +24796,7 @@
     <row r="296">
       <c r="B296" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C296" s="32" t="inlineStr">
@@ -24820,7 +24820,7 @@
     <row r="297">
       <c r="B297" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C297" s="32" t="inlineStr">
@@ -24844,7 +24844,7 @@
     <row r="298">
       <c r="B298" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C298" s="32" t="inlineStr">
@@ -24868,7 +24868,7 @@
     <row r="299">
       <c r="B299" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C299" s="32" t="inlineStr">
@@ -24892,7 +24892,7 @@
     <row r="300">
       <c r="B300" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C300" s="32" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="301">
       <c r="B301" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C301" s="32" t="inlineStr">
@@ -24940,7 +24940,7 @@
     <row r="302">
       <c r="B302" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C302" s="32" t="inlineStr">
@@ -24964,7 +24964,7 @@
     <row r="303">
       <c r="B303" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C303" s="32" t="inlineStr">
@@ -24988,7 +24988,7 @@
     <row r="304">
       <c r="B304" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C304" s="32" t="inlineStr">
@@ -25012,7 +25012,7 @@
     <row r="305">
       <c r="B305" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C305" s="32" t="inlineStr">
@@ -25036,7 +25036,7 @@
     <row r="306">
       <c r="B306" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C306" s="32" t="inlineStr">
@@ -25060,7 +25060,7 @@
     <row r="307">
       <c r="B307" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C307" s="32" t="inlineStr">
@@ -25084,7 +25084,7 @@
     <row r="308">
       <c r="B308" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C308" s="32" t="inlineStr">
@@ -25108,7 +25108,7 @@
     <row r="309">
       <c r="B309" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C309" s="32" t="inlineStr">
@@ -25132,7 +25132,7 @@
     <row r="310">
       <c r="B310" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C310" s="32" t="inlineStr">
@@ -25156,7 +25156,7 @@
     <row r="311">
       <c r="B311" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C311" s="32" t="inlineStr">
@@ -25180,7 +25180,7 @@
     <row r="312">
       <c r="B312" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C312" s="32" t="inlineStr">
@@ -25204,7 +25204,7 @@
     <row r="313">
       <c r="B313" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C313" s="32" t="inlineStr">
@@ -25228,7 +25228,7 @@
     <row r="314">
       <c r="B314" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C314" s="32" t="inlineStr">
@@ -25252,7 +25252,7 @@
     <row r="315">
       <c r="B315" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C315" s="32" t="inlineStr">
@@ -25276,7 +25276,7 @@
     <row r="316">
       <c r="B316" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C316" s="32" t="inlineStr">
@@ -25300,7 +25300,7 @@
     <row r="317">
       <c r="B317" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C317" s="32" t="inlineStr">
@@ -25324,7 +25324,7 @@
     <row r="318">
       <c r="B318" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C318" s="32" t="inlineStr">
@@ -25348,7 +25348,7 @@
     <row r="319">
       <c r="B319" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C319" s="32" t="inlineStr">
@@ -25372,7 +25372,7 @@
     <row r="320">
       <c r="B320" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C320" s="32" t="inlineStr">
@@ -25396,7 +25396,7 @@
     <row r="321">
       <c r="B321" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C321" s="32" t="inlineStr">
@@ -25420,7 +25420,7 @@
     <row r="322">
       <c r="B322" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C322" s="32" t="inlineStr">
@@ -25444,7 +25444,7 @@
     <row r="323">
       <c r="B323" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C323" s="32" t="inlineStr">
@@ -25468,7 +25468,7 @@
     <row r="324">
       <c r="B324" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C324" s="32" t="inlineStr">
@@ -25492,7 +25492,7 @@
     <row r="325">
       <c r="B325" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C325" s="32" t="inlineStr">
@@ -25516,7 +25516,7 @@
     <row r="326">
       <c r="B326" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C326" s="32" t="inlineStr">
@@ -25540,7 +25540,7 @@
     <row r="327">
       <c r="B327" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C327" s="32" t="inlineStr">
@@ -25564,7 +25564,7 @@
     <row r="328">
       <c r="B328" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C328" s="32" t="inlineStr">
@@ -25588,7 +25588,7 @@
     <row r="329">
       <c r="B329" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C329" s="32" t="inlineStr">
@@ -25612,7 +25612,7 @@
     <row r="330">
       <c r="B330" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C330" s="32" t="inlineStr">
@@ -25636,7 +25636,7 @@
     <row r="331">
       <c r="B331" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C331" s="32" t="inlineStr">
@@ -25660,7 +25660,7 @@
     <row r="332">
       <c r="B332" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C332" s="32" t="inlineStr">
@@ -25684,7 +25684,7 @@
     <row r="333">
       <c r="B333" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C333" s="32" t="inlineStr">
@@ -25708,7 +25708,7 @@
     <row r="334">
       <c r="B334" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C334" s="32" t="inlineStr">
@@ -25732,7 +25732,7 @@
     <row r="335">
       <c r="B335" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C335" s="32" t="inlineStr">
@@ -25756,7 +25756,7 @@
     <row r="336">
       <c r="B336" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C336" s="32" t="inlineStr">
@@ -25780,7 +25780,7 @@
     <row r="337">
       <c r="B337" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C337" s="32" t="inlineStr">
@@ -25804,7 +25804,7 @@
     <row r="338">
       <c r="B338" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C338" s="32" t="inlineStr">
@@ -25828,7 +25828,7 @@
     <row r="339">
       <c r="B339" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C339" s="32" t="inlineStr">
@@ -25852,7 +25852,7 @@
     <row r="340">
       <c r="B340" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C340" s="32" t="inlineStr">
@@ -25876,7 +25876,7 @@
     <row r="341">
       <c r="B341" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C341" s="32" t="inlineStr">
@@ -25900,7 +25900,7 @@
     <row r="342">
       <c r="B342" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C342" s="32" t="inlineStr">
@@ -25924,7 +25924,7 @@
     <row r="343">
       <c r="B343" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C343" s="32" t="inlineStr">
@@ -25948,7 +25948,7 @@
     <row r="344">
       <c r="B344" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C344" s="32" t="inlineStr">
@@ -25972,7 +25972,7 @@
     <row r="345">
       <c r="B345" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C345" s="32" t="inlineStr">
@@ -25996,7 +25996,7 @@
     <row r="346">
       <c r="B346" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C346" s="32" t="inlineStr">
@@ -26020,7 +26020,7 @@
     <row r="347">
       <c r="B347" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C347" s="32" t="inlineStr">
@@ -26044,7 +26044,7 @@
     <row r="348">
       <c r="B348" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C348" s="32" t="inlineStr">
@@ -26068,7 +26068,7 @@
     <row r="349">
       <c r="B349" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C349" s="32" t="inlineStr">
@@ -26092,7 +26092,7 @@
     <row r="350">
       <c r="B350" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C350" s="32" t="inlineStr">
@@ -26116,7 +26116,7 @@
     <row r="351">
       <c r="B351" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C351" s="32" t="inlineStr">
@@ -26140,7 +26140,7 @@
     <row r="352">
       <c r="B352" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C352" s="32" t="inlineStr">
@@ -26164,7 +26164,7 @@
     <row r="353">
       <c r="B353" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C353" s="32" t="inlineStr">
@@ -26188,7 +26188,7 @@
     <row r="354">
       <c r="B354" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C354" s="32" t="inlineStr">
@@ -26212,7 +26212,7 @@
     <row r="355">
       <c r="B355" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C355" s="32" t="inlineStr">
@@ -26236,7 +26236,7 @@
     <row r="356">
       <c r="B356" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C356" s="32" t="inlineStr">
@@ -26260,7 +26260,7 @@
     <row r="357">
       <c r="B357" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C357" s="32" t="inlineStr">
@@ -26284,7 +26284,7 @@
     <row r="358">
       <c r="B358" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C358" s="32" t="inlineStr">
@@ -26308,7 +26308,7 @@
     <row r="359">
       <c r="B359" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C359" s="32" t="inlineStr">
@@ -26332,7 +26332,7 @@
     <row r="360">
       <c r="B360" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C360" s="32" t="inlineStr">
@@ -26356,7 +26356,7 @@
     <row r="361">
       <c r="B361" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C361" s="32" t="inlineStr">
@@ -26380,7 +26380,7 @@
     <row r="362">
       <c r="B362" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C362" s="32" t="inlineStr">
@@ -26404,7 +26404,7 @@
     <row r="363">
       <c r="B363" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C363" s="32" t="inlineStr">
@@ -26428,7 +26428,7 @@
     <row r="364">
       <c r="B364" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C364" s="32" t="inlineStr">
@@ -26452,7 +26452,7 @@
     <row r="365">
       <c r="B365" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C365" s="32" t="inlineStr">
@@ -26476,7 +26476,7 @@
     <row r="366">
       <c r="B366" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C366" s="32" t="inlineStr">
@@ -26500,7 +26500,7 @@
     <row r="367">
       <c r="B367" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C367" s="32" t="inlineStr">
@@ -26524,7 +26524,7 @@
     <row r="368">
       <c r="B368" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C368" s="32" t="inlineStr">
@@ -26548,7 +26548,7 @@
     <row r="369">
       <c r="B369" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C369" s="32" t="inlineStr">
@@ -26572,7 +26572,7 @@
     <row r="370">
       <c r="B370" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C370" s="32" t="inlineStr">
@@ -26596,7 +26596,7 @@
     <row r="371">
       <c r="B371" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C371" s="32" t="inlineStr">
@@ -26620,7 +26620,7 @@
     <row r="372">
       <c r="B372" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C372" s="32" t="inlineStr">
@@ -26644,7 +26644,7 @@
     <row r="373">
       <c r="B373" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C373" s="32" t="inlineStr">
@@ -26668,7 +26668,7 @@
     <row r="374">
       <c r="B374" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C374" s="32" t="inlineStr">
@@ -26692,7 +26692,7 @@
     <row r="375">
       <c r="B375" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C375" s="32" t="inlineStr">
@@ -26716,7 +26716,7 @@
     <row r="376">
       <c r="B376" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C376" s="32" t="inlineStr">
@@ -26740,7 +26740,7 @@
     <row r="377">
       <c r="B377" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C377" s="32" t="inlineStr">
@@ -26764,7 +26764,7 @@
     <row r="378">
       <c r="B378" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C378" s="32" t="inlineStr">
@@ -26788,7 +26788,7 @@
     <row r="379">
       <c r="B379" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C379" s="32" t="inlineStr">
@@ -26812,7 +26812,7 @@
     <row r="380">
       <c r="B380" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C380" s="32" t="inlineStr">
@@ -26836,7 +26836,7 @@
     <row r="381">
       <c r="B381" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C381" s="32" t="inlineStr">
@@ -26860,7 +26860,7 @@
     <row r="382">
       <c r="B382" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C382" s="32" t="inlineStr">
@@ -26884,7 +26884,7 @@
     <row r="383">
       <c r="B383" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C383" s="32" t="inlineStr">
@@ -26908,7 +26908,7 @@
     <row r="384">
       <c r="B384" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C384" s="32" t="inlineStr">
@@ -26932,7 +26932,7 @@
     <row r="385">
       <c r="B385" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C385" s="32" t="inlineStr">
@@ -26956,7 +26956,7 @@
     <row r="386">
       <c r="B386" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C386" s="32" t="inlineStr">
@@ -26980,7 +26980,7 @@
     <row r="387">
       <c r="B387" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C387" s="32" t="inlineStr">
@@ -27004,7 +27004,7 @@
     <row r="388">
       <c r="B388" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C388" s="32" t="inlineStr">
@@ -27028,7 +27028,7 @@
     <row r="389">
       <c r="B389" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C389" s="32" t="inlineStr">
@@ -27052,7 +27052,7 @@
     <row r="390">
       <c r="B390" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C390" s="32" t="inlineStr">
@@ -27076,7 +27076,7 @@
     <row r="391">
       <c r="B391" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C391" s="32" t="inlineStr">
@@ -27100,7 +27100,7 @@
     <row r="392">
       <c r="B392" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C392" s="32" t="inlineStr">
@@ -27124,7 +27124,7 @@
     <row r="393">
       <c r="B393" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C393" s="32" t="inlineStr">
@@ -27148,7 +27148,7 @@
     <row r="394">
       <c r="B394" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C394" s="32" t="inlineStr">
@@ -27172,7 +27172,7 @@
     <row r="395">
       <c r="B395" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C395" s="32" t="inlineStr">
@@ -27196,7 +27196,7 @@
     <row r="396">
       <c r="B396" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C396" s="32" t="inlineStr">
@@ -27220,7 +27220,7 @@
     <row r="397">
       <c r="B397" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C397" s="32" t="inlineStr">
@@ -27244,7 +27244,7 @@
     <row r="398">
       <c r="B398" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C398" s="32" t="inlineStr">
@@ -27268,7 +27268,7 @@
     <row r="399">
       <c r="B399" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C399" s="32" t="inlineStr">
@@ -27292,7 +27292,7 @@
     <row r="400">
       <c r="B400" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C400" s="32" t="inlineStr">
@@ -27316,7 +27316,7 @@
     <row r="401">
       <c r="B401" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C401" s="32" t="inlineStr">
@@ -27340,7 +27340,7 @@
     <row r="402">
       <c r="B402" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C402" s="32" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="403">
       <c r="B403" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C403" s="32" t="inlineStr">
@@ -27388,7 +27388,7 @@
     <row r="404">
       <c r="B404" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C404" s="32" t="inlineStr">
@@ -27412,7 +27412,7 @@
     <row r="405">
       <c r="B405" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C405" s="32" t="inlineStr">
@@ -27436,7 +27436,7 @@
     <row r="406">
       <c r="B406" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C406" s="32" t="inlineStr">
@@ -27460,7 +27460,7 @@
     <row r="407">
       <c r="B407" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C407" s="32" t="inlineStr">
@@ -27484,7 +27484,7 @@
     <row r="408">
       <c r="B408" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C408" s="32" t="inlineStr">
@@ -27508,7 +27508,7 @@
     <row r="409">
       <c r="B409" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C409" s="32" t="inlineStr">
@@ -27532,7 +27532,7 @@
     <row r="410">
       <c r="B410" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C410" s="32" t="inlineStr">
@@ -27556,7 +27556,7 @@
     <row r="411">
       <c r="B411" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C411" s="32" t="inlineStr">
@@ -27580,7 +27580,7 @@
     <row r="412">
       <c r="B412" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C412" s="32" t="inlineStr">
@@ -27604,7 +27604,7 @@
     <row r="413">
       <c r="B413" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C413" s="32" t="inlineStr">
@@ -27628,7 +27628,7 @@
     <row r="414">
       <c r="B414" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C414" s="32" t="inlineStr">
@@ -27652,7 +27652,7 @@
     <row r="415">
       <c r="B415" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C415" s="32" t="inlineStr">
@@ -27676,7 +27676,7 @@
     <row r="416">
       <c r="B416" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C416" s="32" t="inlineStr">
@@ -27700,7 +27700,7 @@
     <row r="417">
       <c r="B417" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C417" s="32" t="inlineStr">
@@ -27724,7 +27724,7 @@
     <row r="418">
       <c r="B418" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C418" s="32" t="inlineStr">
@@ -27748,7 +27748,7 @@
     <row r="419">
       <c r="B419" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C419" s="32" t="inlineStr">
@@ -27772,7 +27772,7 @@
     <row r="420">
       <c r="B420" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C420" s="32" t="inlineStr">
@@ -27796,7 +27796,7 @@
     <row r="421">
       <c r="B421" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C421" s="32" t="inlineStr">
@@ -27820,7 +27820,7 @@
     <row r="422">
       <c r="B422" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C422" s="32" t="inlineStr">
@@ -27844,7 +27844,7 @@
     <row r="423">
       <c r="B423" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C423" s="32" t="inlineStr">
@@ -27868,7 +27868,7 @@
     <row r="424">
       <c r="B424" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C424" s="32" t="inlineStr">
@@ -27892,7 +27892,7 @@
     <row r="425">
       <c r="B425" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C425" s="32" t="inlineStr">
@@ -27916,7 +27916,7 @@
     <row r="426">
       <c r="B426" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C426" s="32" t="inlineStr">
@@ -27940,7 +27940,7 @@
     <row r="427">
       <c r="B427" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C427" s="32" t="inlineStr">
@@ -27964,7 +27964,7 @@
     <row r="428">
       <c r="B428" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C428" s="32" t="inlineStr">
@@ -27988,7 +27988,7 @@
     <row r="429">
       <c r="B429" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C429" s="32" t="inlineStr">
@@ -28012,7 +28012,7 @@
     <row r="430">
       <c r="B430" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C430" s="32" t="inlineStr">
@@ -28036,7 +28036,7 @@
     <row r="431">
       <c r="B431" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C431" s="32" t="inlineStr">
@@ -28060,7 +28060,7 @@
     <row r="432">
       <c r="B432" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C432" s="32" t="inlineStr">
@@ -28084,7 +28084,7 @@
     <row r="433">
       <c r="B433" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C433" s="32" t="inlineStr">
@@ -28108,7 +28108,7 @@
     <row r="434">
       <c r="B434" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C434" s="32" t="inlineStr">
@@ -28132,7 +28132,7 @@
     <row r="435">
       <c r="B435" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C435" s="32" t="inlineStr">
@@ -28156,7 +28156,7 @@
     <row r="436">
       <c r="B436" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C436" s="32" t="inlineStr">
@@ -28180,7 +28180,7 @@
     <row r="437">
       <c r="B437" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C437" s="32" t="inlineStr">
@@ -28204,7 +28204,7 @@
     <row r="438">
       <c r="B438" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C438" s="32" t="inlineStr">
@@ -28228,7 +28228,7 @@
     <row r="439">
       <c r="B439" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C439" s="32" t="inlineStr">
@@ -28252,7 +28252,7 @@
     <row r="440">
       <c r="B440" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C440" s="32" t="inlineStr">
@@ -28276,7 +28276,7 @@
     <row r="441">
       <c r="B441" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C441" s="32" t="inlineStr">
@@ -28300,7 +28300,7 @@
     <row r="442">
       <c r="B442" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C442" s="32" t="inlineStr">
@@ -28324,7 +28324,7 @@
     <row r="443">
       <c r="B443" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C443" s="32" t="inlineStr">
@@ -28348,7 +28348,7 @@
     <row r="444">
       <c r="B444" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C444" s="32" t="inlineStr">
@@ -28372,7 +28372,7 @@
     <row r="445">
       <c r="B445" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C445" s="32" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="446">
       <c r="B446" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C446" s="32" t="inlineStr">
@@ -28420,7 +28420,7 @@
     <row r="447">
       <c r="B447" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C447" s="32" t="inlineStr">
@@ -28444,7 +28444,7 @@
     <row r="448">
       <c r="B448" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C448" s="32" t="inlineStr">
@@ -28468,7 +28468,7 @@
     <row r="449">
       <c r="B449" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C449" s="32" t="inlineStr">
@@ -28492,7 +28492,7 @@
     <row r="450">
       <c r="B450" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C450" s="32" t="inlineStr">
@@ -28516,7 +28516,7 @@
     <row r="451">
       <c r="B451" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C451" s="32" t="inlineStr">
@@ -28540,7 +28540,7 @@
     <row r="452">
       <c r="B452" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C452" s="32" t="inlineStr">
@@ -28564,7 +28564,7 @@
     <row r="453">
       <c r="B453" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C453" s="32" t="inlineStr">
@@ -28588,7 +28588,7 @@
     <row r="454">
       <c r="B454" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C454" s="32" t="inlineStr">
@@ -28612,7 +28612,7 @@
     <row r="455">
       <c r="B455" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C455" s="32" t="inlineStr">
@@ -28636,7 +28636,7 @@
     <row r="456">
       <c r="B456" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C456" s="32" t="inlineStr">
@@ -28660,7 +28660,7 @@
     <row r="457">
       <c r="B457" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C457" s="32" t="inlineStr">
@@ -28684,7 +28684,7 @@
     <row r="458">
       <c r="B458" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C458" s="32" t="inlineStr">
@@ -28708,7 +28708,7 @@
     <row r="459">
       <c r="B459" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C459" s="32" t="inlineStr">
@@ -28732,7 +28732,7 @@
     <row r="460">
       <c r="B460" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C460" s="32" t="inlineStr">
@@ -28756,7 +28756,7 @@
     <row r="461">
       <c r="B461" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C461" s="32" t="inlineStr">
@@ -28780,7 +28780,7 @@
     <row r="462">
       <c r="B462" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C462" s="32" t="inlineStr">
@@ -28804,7 +28804,7 @@
     <row r="463">
       <c r="B463" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C463" s="32" t="inlineStr">
@@ -28828,7 +28828,7 @@
     <row r="464">
       <c r="B464" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C464" s="32" t="inlineStr">
@@ -28852,7 +28852,7 @@
     <row r="465">
       <c r="B465" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C465" s="32" t="inlineStr">
@@ -28876,7 +28876,7 @@
     <row r="466">
       <c r="B466" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C466" s="32" t="inlineStr">
@@ -28900,7 +28900,7 @@
     <row r="467">
       <c r="B467" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C467" s="32" t="inlineStr">
@@ -28924,7 +28924,7 @@
     <row r="468">
       <c r="B468" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C468" s="32" t="inlineStr">
@@ -28948,7 +28948,7 @@
     <row r="469">
       <c r="B469" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C469" s="32" t="inlineStr">
@@ -28972,7 +28972,7 @@
     <row r="470">
       <c r="B470" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C470" s="32" t="inlineStr">
@@ -28996,7 +28996,7 @@
     <row r="471">
       <c r="B471" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C471" s="32" t="inlineStr">
@@ -29020,7 +29020,7 @@
     <row r="472">
       <c r="B472" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C472" s="32" t="inlineStr">
@@ -29044,7 +29044,7 @@
     <row r="473">
       <c r="B473" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C473" s="32" t="inlineStr">
@@ -29068,7 +29068,7 @@
     <row r="474">
       <c r="B474" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C474" s="32" t="inlineStr">
@@ -29092,7 +29092,7 @@
     <row r="475">
       <c r="B475" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C475" s="32" t="inlineStr">
@@ -29116,7 +29116,7 @@
     <row r="476">
       <c r="B476" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C476" s="32" t="inlineStr">
@@ -29140,7 +29140,7 @@
     <row r="477">
       <c r="B477" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C477" s="32" t="inlineStr">
@@ -29164,7 +29164,7 @@
     <row r="478">
       <c r="B478" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C478" s="32" t="inlineStr">
@@ -29188,7 +29188,7 @@
     <row r="479">
       <c r="B479" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C479" s="32" t="inlineStr">
@@ -29212,7 +29212,7 @@
     <row r="480">
       <c r="B480" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C480" s="32" t="inlineStr">
@@ -29236,7 +29236,7 @@
     <row r="481">
       <c r="B481" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C481" s="32" t="inlineStr">
@@ -29260,7 +29260,7 @@
     <row r="482">
       <c r="B482" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C482" s="32" t="inlineStr">
@@ -29284,7 +29284,7 @@
     <row r="483">
       <c r="B483" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C483" s="32" t="inlineStr">
@@ -29308,7 +29308,7 @@
     <row r="484">
       <c r="B484" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C484" s="32" t="inlineStr">
@@ -29332,7 +29332,7 @@
     <row r="485">
       <c r="B485" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C485" s="32" t="inlineStr">
@@ -29356,7 +29356,7 @@
     <row r="486">
       <c r="B486" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C486" s="32" t="inlineStr">
@@ -29380,7 +29380,7 @@
     <row r="487">
       <c r="B487" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C487" s="32" t="inlineStr">
@@ -29404,7 +29404,7 @@
     <row r="488">
       <c r="B488" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C488" s="32" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="489">
       <c r="B489" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C489" s="32" t="inlineStr">
@@ -29452,7 +29452,7 @@
     <row r="490">
       <c r="B490" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C490" s="32" t="inlineStr">
@@ -29476,7 +29476,7 @@
     <row r="491">
       <c r="B491" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C491" s="32" t="inlineStr">
@@ -29500,7 +29500,7 @@
     <row r="492">
       <c r="B492" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C492" s="32" t="inlineStr">
@@ -29524,7 +29524,7 @@
     <row r="493">
       <c r="B493" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C493" s="32" t="inlineStr">
@@ -29548,7 +29548,7 @@
     <row r="494">
       <c r="B494" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C494" s="32" t="inlineStr">
@@ -29572,7 +29572,7 @@
     <row r="495">
       <c r="B495" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C495" s="32" t="inlineStr">
@@ -29596,7 +29596,7 @@
     <row r="496">
       <c r="B496" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C496" s="32" t="inlineStr">
@@ -29620,7 +29620,7 @@
     <row r="497">
       <c r="B497" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C497" s="32" t="inlineStr">
@@ -29644,7 +29644,7 @@
     <row r="498">
       <c r="B498" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C498" s="32" t="inlineStr">
@@ -29668,7 +29668,7 @@
     <row r="499">
       <c r="B499" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C499" s="32" t="inlineStr">
@@ -29692,7 +29692,7 @@
     <row r="500">
       <c r="B500" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C500" s="32" t="inlineStr">
@@ -29716,7 +29716,7 @@
     <row r="501">
       <c r="B501" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C501" s="32" t="inlineStr">
@@ -29740,7 +29740,7 @@
     <row r="502">
       <c r="B502" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C502" s="32" t="inlineStr">
@@ -29764,7 +29764,7 @@
     <row r="503">
       <c r="B503" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C503" s="32" t="inlineStr">
@@ -29788,7 +29788,7 @@
     <row r="504">
       <c r="B504" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C504" s="32" t="inlineStr">
@@ -29812,7 +29812,7 @@
     <row r="505">
       <c r="B505" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C505" s="32" t="inlineStr">
@@ -29836,7 +29836,7 @@
     <row r="506">
       <c r="B506" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C506" s="32" t="inlineStr">
@@ -29860,7 +29860,7 @@
     <row r="507">
       <c r="B507" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C507" s="32" t="inlineStr">
@@ -29884,7 +29884,7 @@
     <row r="508">
       <c r="B508" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C508" s="32" t="inlineStr">
@@ -29908,7 +29908,7 @@
     <row r="509">
       <c r="B509" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C509" s="32" t="inlineStr">
@@ -29932,7 +29932,7 @@
     <row r="510">
       <c r="B510" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C510" s="32" t="inlineStr">
@@ -29956,7 +29956,7 @@
     <row r="511">
       <c r="B511" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C511" s="32" t="inlineStr">
@@ -29980,7 +29980,7 @@
     <row r="512">
       <c r="B512" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C512" s="32" t="inlineStr">
@@ -30004,7 +30004,7 @@
     <row r="513">
       <c r="B513" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C513" s="32" t="inlineStr">
@@ -30028,7 +30028,7 @@
     <row r="514">
       <c r="B514" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C514" s="32" t="inlineStr">
@@ -30052,7 +30052,7 @@
     <row r="515">
       <c r="B515" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C515" s="32" t="inlineStr">
@@ -30076,7 +30076,7 @@
     <row r="516">
       <c r="B516" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C516" s="32" t="inlineStr">
@@ -30100,7 +30100,7 @@
     <row r="517">
       <c r="B517" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C517" s="32" t="inlineStr">
@@ -30124,7 +30124,7 @@
     <row r="518">
       <c r="B518" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C518" s="32" t="inlineStr">
@@ -30148,7 +30148,7 @@
     <row r="519">
       <c r="B519" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C519" s="32" t="inlineStr">
@@ -30172,7 +30172,7 @@
     <row r="520">
       <c r="B520" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C520" s="32" t="inlineStr">
@@ -30196,7 +30196,7 @@
     <row r="521">
       <c r="B521" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C521" s="32" t="inlineStr">
@@ -30220,7 +30220,7 @@
     <row r="522">
       <c r="B522" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C522" s="32" t="inlineStr">
@@ -30244,7 +30244,7 @@
     <row r="523">
       <c r="B523" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C523" s="32" t="inlineStr">
@@ -30268,7 +30268,7 @@
     <row r="524">
       <c r="B524" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C524" s="32" t="inlineStr">
@@ -30292,7 +30292,7 @@
     <row r="525">
       <c r="B525" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C525" s="32" t="inlineStr">
@@ -30316,7 +30316,7 @@
     <row r="526">
       <c r="B526" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C526" s="32" t="inlineStr">
@@ -30340,7 +30340,7 @@
     <row r="527">
       <c r="B527" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C527" s="32" t="inlineStr">
@@ -30364,7 +30364,7 @@
     <row r="528">
       <c r="B528" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C528" s="32" t="inlineStr">
@@ -30388,7 +30388,7 @@
     <row r="529">
       <c r="B529" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C529" s="32" t="inlineStr">
@@ -30412,7 +30412,7 @@
     <row r="530">
       <c r="B530" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C530" s="32" t="inlineStr">
@@ -30436,7 +30436,7 @@
     <row r="531">
       <c r="B531" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C531" s="32" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="532">
       <c r="B532" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C532" s="32" t="inlineStr">
@@ -30484,7 +30484,7 @@
     <row r="533">
       <c r="B533" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C533" s="32" t="inlineStr">
@@ -30508,7 +30508,7 @@
     <row r="534">
       <c r="B534" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C534" s="32" t="inlineStr">
@@ -30532,7 +30532,7 @@
     <row r="535">
       <c r="B535" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C535" s="32" t="inlineStr">
@@ -30556,7 +30556,7 @@
     <row r="536">
       <c r="B536" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C536" s="32" t="inlineStr">
@@ -30580,7 +30580,7 @@
     <row r="537">
       <c r="B537" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C537" s="32" t="inlineStr">
@@ -30604,7 +30604,7 @@
     <row r="538">
       <c r="B538" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C538" s="32" t="inlineStr">
@@ -30628,7 +30628,7 @@
     <row r="539">
       <c r="B539" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C539" s="32" t="inlineStr">
@@ -30652,7 +30652,7 @@
     <row r="540">
       <c r="B540" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C540" s="32" t="inlineStr">
@@ -30676,7 +30676,7 @@
     <row r="541">
       <c r="B541" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C541" s="32" t="inlineStr">
@@ -30700,7 +30700,7 @@
     <row r="542">
       <c r="B542" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C542" s="32" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="543">
       <c r="B543" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C543" s="32" t="inlineStr">
@@ -30748,7 +30748,7 @@
     <row r="544">
       <c r="B544" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C544" s="32" t="inlineStr">
@@ -30772,7 +30772,7 @@
     <row r="545">
       <c r="B545" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C545" s="32" t="inlineStr">
@@ -30796,7 +30796,7 @@
     <row r="546">
       <c r="B546" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C546" s="32" t="inlineStr">
@@ -30820,7 +30820,7 @@
     <row r="547">
       <c r="B547" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C547" s="32" t="inlineStr">
@@ -30844,7 +30844,7 @@
     <row r="548">
       <c r="B548" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C548" s="32" t="inlineStr">
@@ -30868,7 +30868,7 @@
     <row r="549">
       <c r="B549" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C549" s="32" t="inlineStr">
@@ -30892,7 +30892,7 @@
     <row r="550">
       <c r="B550" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C550" s="32" t="inlineStr">
@@ -30916,7 +30916,7 @@
     <row r="551">
       <c r="B551" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C551" s="32" t="inlineStr">
@@ -30940,7 +30940,7 @@
     <row r="552">
       <c r="B552" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C552" s="32" t="inlineStr">
@@ -30964,7 +30964,7 @@
     <row r="553">
       <c r="B553" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C553" s="32" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="554">
       <c r="B554" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C554" s="32" t="inlineStr">
@@ -31012,7 +31012,7 @@
     <row r="555">
       <c r="B555" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C555" s="32" t="inlineStr">
@@ -31036,7 +31036,7 @@
     <row r="556">
       <c r="B556" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C556" s="32" t="inlineStr">
@@ -31060,7 +31060,7 @@
     <row r="557">
       <c r="B557" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C557" s="32" t="inlineStr">
@@ -31084,7 +31084,7 @@
     <row r="558">
       <c r="B558" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C558" s="32" t="inlineStr">
@@ -31108,7 +31108,7 @@
     <row r="559">
       <c r="B559" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C559" s="32" t="inlineStr">
@@ -31132,7 +31132,7 @@
     <row r="560">
       <c r="B560" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C560" s="32" t="inlineStr">
@@ -31156,7 +31156,7 @@
     <row r="561">
       <c r="B561" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C561" s="32" t="inlineStr">
@@ -31180,7 +31180,7 @@
     <row r="562">
       <c r="B562" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C562" s="32" t="inlineStr">
@@ -31204,7 +31204,7 @@
     <row r="563">
       <c r="B563" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C563" s="32" t="inlineStr">
@@ -31228,7 +31228,7 @@
     <row r="564">
       <c r="B564" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C564" s="32" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="565">
       <c r="B565" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C565" s="32" t="inlineStr">
@@ -31276,7 +31276,7 @@
     <row r="566">
       <c r="B566" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C566" s="32" t="inlineStr">
@@ -31300,7 +31300,7 @@
     <row r="567">
       <c r="B567" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C567" s="32" t="inlineStr">
@@ -31324,7 +31324,7 @@
     <row r="568">
       <c r="B568" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C568" s="32" t="inlineStr">
@@ -31348,7 +31348,7 @@
     <row r="569">
       <c r="B569" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C569" s="32" t="inlineStr">
@@ -31372,7 +31372,7 @@
     <row r="570">
       <c r="B570" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C570" s="32" t="inlineStr">
@@ -31396,7 +31396,7 @@
     <row r="571">
       <c r="B571" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C571" s="32" t="inlineStr">
@@ -31420,7 +31420,7 @@
     <row r="572">
       <c r="B572" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C572" s="32" t="inlineStr">
@@ -31444,7 +31444,7 @@
     <row r="573">
       <c r="B573" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C573" s="32" t="inlineStr">
@@ -31468,7 +31468,7 @@
     <row r="574">
       <c r="B574" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C574" s="32" t="inlineStr">
@@ -31492,7 +31492,7 @@
     <row r="575">
       <c r="B575" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C575" s="32" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="576">
       <c r="B576" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C576" s="32" t="inlineStr">
@@ -31540,7 +31540,7 @@
     <row r="577">
       <c r="B577" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C577" s="32" t="inlineStr">
@@ -31564,7 +31564,7 @@
     <row r="578">
       <c r="B578" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C578" s="32" t="inlineStr">
@@ -31588,7 +31588,7 @@
     <row r="579">
       <c r="B579" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C579" s="32" t="inlineStr">
@@ -31612,7 +31612,7 @@
     <row r="580">
       <c r="B580" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C580" s="32" t="inlineStr">
@@ -31636,7 +31636,7 @@
     <row r="581">
       <c r="B581" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C581" s="32" t="inlineStr">
@@ -31660,7 +31660,7 @@
     <row r="582">
       <c r="B582" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C582" s="32" t="inlineStr">
@@ -31684,7 +31684,7 @@
     <row r="583">
       <c r="B583" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C583" s="32" t="inlineStr">
@@ -31708,7 +31708,7 @@
     <row r="584">
       <c r="B584" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C584" s="32" t="inlineStr">
@@ -31732,7 +31732,7 @@
     <row r="585">
       <c r="B585" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C585" s="32" t="inlineStr">
@@ -31756,7 +31756,7 @@
     <row r="586">
       <c r="B586" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C586" s="32" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="587">
       <c r="B587" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C587" s="32" t="inlineStr">
@@ -31804,7 +31804,7 @@
     <row r="588">
       <c r="B588" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C588" s="32" t="inlineStr">
@@ -31828,7 +31828,7 @@
     <row r="589">
       <c r="B589" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C589" s="32" t="inlineStr">
@@ -31852,7 +31852,7 @@
     <row r="590">
       <c r="B590" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C590" s="32" t="inlineStr">
@@ -31876,7 +31876,7 @@
     <row r="591">
       <c r="B591" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C591" s="32" t="inlineStr">
@@ -31900,7 +31900,7 @@
     <row r="592">
       <c r="B592" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C592" s="32" t="inlineStr">
@@ -31924,7 +31924,7 @@
     <row r="593">
       <c r="B593" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C593" s="32" t="inlineStr">
@@ -31948,7 +31948,7 @@
     <row r="594">
       <c r="B594" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C594" s="32" t="inlineStr">
@@ -31972,7 +31972,7 @@
     <row r="595">
       <c r="B595" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C595" s="32" t="inlineStr">
@@ -31996,7 +31996,7 @@
     <row r="596">
       <c r="B596" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C596" s="32" t="inlineStr">
@@ -32020,7 +32020,7 @@
     <row r="597">
       <c r="B597" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C597" s="32" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="598">
       <c r="B598" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C598" s="32" t="inlineStr">
@@ -32068,7 +32068,7 @@
     <row r="599">
       <c r="B599" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C599" s="32" t="inlineStr">
@@ -32092,7 +32092,7 @@
     <row r="600">
       <c r="B600" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C600" s="32" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <row r="601">
       <c r="B601" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C601" s="32" t="inlineStr">
@@ -32140,7 +32140,7 @@
     <row r="602">
       <c r="B602" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C602" s="32" t="inlineStr">
@@ -32164,7 +32164,7 @@
     <row r="603">
       <c r="B603" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C603" s="32" t="inlineStr">
@@ -32188,7 +32188,7 @@
     <row r="604">
       <c r="B604" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C604" s="32" t="inlineStr">
@@ -32212,7 +32212,7 @@
     <row r="605">
       <c r="B605" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C605" s="32" t="inlineStr">
@@ -32236,7 +32236,7 @@
     <row r="606">
       <c r="B606" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C606" s="32" t="inlineStr">
@@ -32260,7 +32260,7 @@
     <row r="607">
       <c r="B607" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C607" s="32" t="inlineStr">
@@ -32284,7 +32284,7 @@
     <row r="608">
       <c r="B608" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C608" s="32" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="609">
       <c r="B609" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C609" s="32" t="inlineStr">
@@ -32332,7 +32332,7 @@
     <row r="610">
       <c r="B610" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C610" s="32" t="inlineStr">
@@ -32356,7 +32356,7 @@
     <row r="611">
       <c r="B611" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C611" s="32" t="inlineStr">
@@ -32380,7 +32380,7 @@
     <row r="612">
       <c r="B612" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C612" s="32" t="inlineStr">
@@ -32404,7 +32404,7 @@
     <row r="613">
       <c r="B613" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C613" s="32" t="inlineStr">
@@ -32428,7 +32428,7 @@
     <row r="614">
       <c r="B614" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C614" s="32" t="inlineStr">
@@ -32452,7 +32452,7 @@
     <row r="615">
       <c r="B615" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C615" s="32" t="inlineStr">
@@ -32476,7 +32476,7 @@
     <row r="616">
       <c r="B616" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C616" s="32" t="inlineStr">
@@ -32500,7 +32500,7 @@
     <row r="617">
       <c r="B617" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C617" s="32" t="inlineStr">
@@ -32524,7 +32524,7 @@
     <row r="618">
       <c r="B618" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C618" s="32" t="inlineStr">
@@ -32548,7 +32548,7 @@
     <row r="619">
       <c r="B619" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C619" s="32" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="620">
       <c r="B620" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C620" s="32" t="inlineStr">
@@ -32596,7 +32596,7 @@
     <row r="621">
       <c r="B621" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C621" s="32" t="inlineStr">
@@ -32620,7 +32620,7 @@
     <row r="622">
       <c r="B622" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C622" s="32" t="inlineStr">
@@ -32644,7 +32644,7 @@
     <row r="623">
       <c r="B623" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C623" s="32" t="inlineStr">
@@ -32668,7 +32668,7 @@
     <row r="624">
       <c r="B624" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C624" s="32" t="inlineStr">
@@ -32692,7 +32692,7 @@
     <row r="625">
       <c r="B625" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C625" s="32" t="inlineStr">
@@ -32716,7 +32716,7 @@
     <row r="626">
       <c r="B626" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C626" s="32" t="inlineStr">
@@ -32740,7 +32740,7 @@
     <row r="627">
       <c r="B627" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C627" s="32" t="inlineStr">
@@ -32764,7 +32764,7 @@
     <row r="628">
       <c r="B628" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C628" s="32" t="inlineStr">
@@ -32788,7 +32788,7 @@
     <row r="629">
       <c r="B629" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C629" s="32" t="inlineStr">
@@ -32812,7 +32812,7 @@
     <row r="630">
       <c r="B630" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C630" s="32" t="inlineStr">
@@ -32836,7 +32836,7 @@
     <row r="631">
       <c r="B631" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C631" s="32" t="inlineStr">
@@ -32860,7 +32860,7 @@
     <row r="632">
       <c r="B632" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C632" s="32" t="inlineStr">
@@ -32884,7 +32884,7 @@
     <row r="633">
       <c r="B633" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C633" s="32" t="inlineStr">
@@ -32908,7 +32908,7 @@
     <row r="634">
       <c r="B634" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C634" s="32" t="inlineStr">
@@ -32932,7 +32932,7 @@
     <row r="635">
       <c r="B635" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C635" s="32" t="inlineStr">
@@ -32956,7 +32956,7 @@
     <row r="636">
       <c r="B636" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C636" s="32" t="inlineStr">
@@ -32980,7 +32980,7 @@
     <row r="637">
       <c r="B637" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C637" s="32" t="inlineStr">
@@ -33004,7 +33004,7 @@
     <row r="638">
       <c r="B638" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C638" s="32" t="inlineStr">
@@ -33028,7 +33028,7 @@
     <row r="639">
       <c r="B639" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C639" s="32" t="inlineStr">
@@ -33052,7 +33052,7 @@
     <row r="640">
       <c r="B640" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C640" s="32" t="inlineStr">
@@ -33076,7 +33076,7 @@
     <row r="641">
       <c r="B641" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C641" s="32" t="inlineStr">
@@ -33100,7 +33100,7 @@
     <row r="642">
       <c r="B642" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C642" s="32" t="inlineStr">
@@ -33124,7 +33124,7 @@
     <row r="643">
       <c r="B643" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C643" s="32" t="inlineStr">
@@ -33148,7 +33148,7 @@
     <row r="644">
       <c r="B644" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C644" s="32" t="inlineStr">
@@ -33172,7 +33172,7 @@
     <row r="645">
       <c r="B645" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C645" s="32" t="inlineStr">
@@ -33196,7 +33196,7 @@
     <row r="646">
       <c r="B646" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C646" s="32" t="inlineStr">
@@ -33220,7 +33220,7 @@
     <row r="647">
       <c r="B647" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C647" s="32" t="inlineStr">
@@ -33244,7 +33244,7 @@
     <row r="648">
       <c r="B648" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C648" s="32" t="inlineStr">
@@ -33268,7 +33268,7 @@
     <row r="649">
       <c r="B649" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C649" s="32" t="inlineStr">
@@ -33292,7 +33292,7 @@
     <row r="650">
       <c r="B650" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C650" s="32" t="inlineStr">
@@ -33316,7 +33316,7 @@
     <row r="651">
       <c r="B651" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C651" s="32" t="inlineStr">
@@ -33340,7 +33340,7 @@
     <row r="652">
       <c r="B652" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C652" s="32" t="inlineStr">
@@ -33364,7 +33364,7 @@
     <row r="653">
       <c r="B653" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C653" s="32" t="inlineStr">
@@ -33388,7 +33388,7 @@
     <row r="654">
       <c r="B654" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C654" s="32" t="inlineStr">
@@ -33412,7 +33412,7 @@
     <row r="655">
       <c r="B655" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C655" s="32" t="inlineStr">
@@ -33436,7 +33436,7 @@
     <row r="656">
       <c r="B656" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C656" s="32" t="inlineStr">
@@ -33460,7 +33460,7 @@
     <row r="657">
       <c r="B657" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C657" s="32" t="inlineStr">
@@ -33484,7 +33484,7 @@
     <row r="658">
       <c r="B658" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C658" s="32" t="inlineStr">
@@ -33508,7 +33508,7 @@
     <row r="659">
       <c r="B659" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C659" s="32" t="inlineStr">
@@ -33532,7 +33532,7 @@
     <row r="660">
       <c r="B660" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C660" s="32" t="inlineStr">
@@ -33556,7 +33556,7 @@
     <row r="661">
       <c r="B661" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C661" s="32" t="inlineStr">
@@ -33580,7 +33580,7 @@
     <row r="662">
       <c r="B662" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C662" s="32" t="inlineStr">
@@ -33604,7 +33604,7 @@
     <row r="663">
       <c r="B663" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C663" s="32" t="inlineStr">
@@ -33628,7 +33628,7 @@
     <row r="664">
       <c r="B664" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C664" s="32" t="inlineStr">
@@ -33652,7 +33652,7 @@
     <row r="665">
       <c r="B665" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C665" s="32" t="inlineStr">
@@ -33676,7 +33676,7 @@
     <row r="666">
       <c r="B666" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C666" s="32" t="inlineStr">
@@ -33700,7 +33700,7 @@
     <row r="667">
       <c r="B667" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C667" s="32" t="inlineStr">
@@ -33724,7 +33724,7 @@
     <row r="668">
       <c r="B668" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C668" s="32" t="inlineStr">
@@ -33748,7 +33748,7 @@
     <row r="669">
       <c r="B669" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C669" s="32" t="inlineStr">
@@ -33772,7 +33772,7 @@
     <row r="670">
       <c r="B670" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C670" s="32" t="inlineStr">
@@ -33796,7 +33796,7 @@
     <row r="671">
       <c r="B671" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C671" s="32" t="inlineStr">
@@ -33820,7 +33820,7 @@
     <row r="672">
       <c r="B672" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C672" s="32" t="inlineStr">
@@ -33844,7 +33844,7 @@
     <row r="673">
       <c r="B673" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C673" s="32" t="inlineStr">
@@ -33868,7 +33868,7 @@
     <row r="674">
       <c r="B674" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C674" s="32" t="inlineStr">
@@ -33892,7 +33892,7 @@
     <row r="675">
       <c r="B675" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C675" s="32" t="inlineStr">
@@ -33916,7 +33916,7 @@
     <row r="676">
       <c r="B676" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C676" s="32" t="inlineStr">
@@ -33940,7 +33940,7 @@
     <row r="677">
       <c r="B677" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C677" s="32" t="inlineStr">
@@ -33964,7 +33964,7 @@
     <row r="678">
       <c r="B678" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C678" s="32" t="inlineStr">
@@ -33988,7 +33988,7 @@
     <row r="679">
       <c r="B679" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C679" s="32" t="inlineStr">
@@ -34012,7 +34012,7 @@
     <row r="680">
       <c r="B680" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C680" s="32" t="inlineStr">
@@ -34036,7 +34036,7 @@
     <row r="681">
       <c r="B681" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C681" s="32" t="inlineStr">
@@ -34060,7 +34060,7 @@
     <row r="682">
       <c r="B682" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C682" s="32" t="inlineStr">
@@ -34084,7 +34084,7 @@
     <row r="683">
       <c r="B683" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C683" s="32" t="inlineStr">
@@ -34108,7 +34108,7 @@
     <row r="684">
       <c r="B684" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C684" s="32" t="inlineStr">
@@ -34132,7 +34132,7 @@
     <row r="685">
       <c r="B685" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C685" s="32" t="inlineStr">
@@ -34156,7 +34156,7 @@
     <row r="686">
       <c r="B686" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C686" s="32" t="inlineStr">
@@ -34180,7 +34180,7 @@
     <row r="687">
       <c r="B687" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C687" s="32" t="inlineStr">
@@ -34204,7 +34204,7 @@
     <row r="688">
       <c r="B688" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C688" s="32" t="inlineStr">
@@ -34228,7 +34228,7 @@
     <row r="689">
       <c r="B689" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C689" s="32" t="inlineStr">
@@ -34252,7 +34252,7 @@
     <row r="690">
       <c r="B690" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C690" s="32" t="inlineStr">
@@ -34276,7 +34276,7 @@
     <row r="691">
       <c r="B691" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C691" s="32" t="inlineStr">
@@ -34300,7 +34300,7 @@
     <row r="692">
       <c r="B692" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C692" s="32" t="inlineStr">
@@ -34324,7 +34324,7 @@
     <row r="693">
       <c r="B693" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C693" s="32" t="inlineStr">
@@ -34348,7 +34348,7 @@
     <row r="694">
       <c r="B694" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C694" s="32" t="inlineStr">
@@ -34372,7 +34372,7 @@
     <row r="695">
       <c r="B695" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C695" s="32" t="inlineStr">
@@ -34396,7 +34396,7 @@
     <row r="696">
       <c r="B696" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C696" s="32" t="inlineStr">
@@ -34420,7 +34420,7 @@
     <row r="697">
       <c r="B697" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C697" s="32" t="inlineStr">
@@ -34444,7 +34444,7 @@
     <row r="698">
       <c r="B698" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C698" s="32" t="inlineStr">
@@ -34468,7 +34468,7 @@
     <row r="699">
       <c r="B699" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C699" s="32" t="inlineStr">
@@ -34492,7 +34492,7 @@
     <row r="700">
       <c r="B700" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C700" s="32" t="inlineStr">
@@ -34516,7 +34516,7 @@
     <row r="701">
       <c r="B701" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C701" s="32" t="inlineStr">
@@ -34540,7 +34540,7 @@
     <row r="702">
       <c r="B702" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C702" s="32" t="inlineStr">
@@ -34564,7 +34564,7 @@
     <row r="703">
       <c r="B703" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C703" s="32" t="inlineStr">
@@ -34588,7 +34588,7 @@
     <row r="704">
       <c r="B704" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C704" s="32" t="inlineStr">
@@ -34612,7 +34612,7 @@
     <row r="705">
       <c r="B705" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C705" s="32" t="inlineStr">
@@ -34636,7 +34636,7 @@
     <row r="706">
       <c r="B706" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C706" s="32" t="inlineStr">
@@ -34660,7 +34660,7 @@
     <row r="707">
       <c r="B707" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C707" s="32" t="inlineStr">
@@ -34684,7 +34684,7 @@
     <row r="708">
       <c r="B708" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C708" s="32" t="inlineStr">
@@ -34708,7 +34708,7 @@
     <row r="709">
       <c r="B709" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C709" s="32" t="inlineStr">
@@ -34732,7 +34732,7 @@
     <row r="710">
       <c r="B710" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C710" s="32" t="inlineStr">
@@ -34756,7 +34756,7 @@
     <row r="711">
       <c r="B711" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C711" s="32" t="inlineStr">
@@ -34780,7 +34780,7 @@
     <row r="712">
       <c r="B712" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C712" s="32" t="inlineStr">
@@ -34804,7 +34804,7 @@
     <row r="713">
       <c r="B713" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C713" s="32" t="inlineStr">
@@ -34828,7 +34828,7 @@
     <row r="714">
       <c r="B714" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C714" s="32" t="inlineStr">
@@ -34852,7 +34852,7 @@
     <row r="715">
       <c r="B715" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C715" s="32" t="inlineStr">
@@ -34876,7 +34876,7 @@
     <row r="716">
       <c r="B716" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C716" s="32" t="inlineStr">
@@ -34900,7 +34900,7 @@
     <row r="717">
       <c r="B717" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C717" s="32" t="inlineStr">
@@ -34924,7 +34924,7 @@
     <row r="718">
       <c r="B718" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C718" s="32" t="inlineStr">
@@ -34948,7 +34948,7 @@
     <row r="719">
       <c r="B719" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C719" s="32" t="inlineStr">
@@ -34972,7 +34972,7 @@
     <row r="720">
       <c r="B720" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C720" s="32" t="inlineStr">
@@ -34996,7 +34996,7 @@
     <row r="721">
       <c r="B721" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C721" s="32" t="inlineStr">
@@ -35020,7 +35020,7 @@
     <row r="722">
       <c r="B722" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C722" s="32" t="inlineStr">
@@ -35044,7 +35044,7 @@
     <row r="723">
       <c r="B723" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C723" s="32" t="inlineStr">
@@ -35068,7 +35068,7 @@
     <row r="724">
       <c r="B724" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C724" s="32" t="inlineStr">
@@ -35092,7 +35092,7 @@
     <row r="725">
       <c r="B725" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C725" s="32" t="inlineStr">
@@ -35116,7 +35116,7 @@
     <row r="726">
       <c r="B726" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C726" s="32" t="inlineStr">
@@ -35140,7 +35140,7 @@
     <row r="727">
       <c r="B727" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C727" s="32" t="inlineStr">
@@ -35164,7 +35164,7 @@
     <row r="728">
       <c r="B728" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C728" s="32" t="inlineStr">
@@ -35188,7 +35188,7 @@
     <row r="729">
       <c r="B729" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C729" s="32" t="inlineStr">
@@ -35212,7 +35212,7 @@
     <row r="730">
       <c r="B730" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C730" s="32" t="inlineStr">
@@ -35236,7 +35236,7 @@
     <row r="731">
       <c r="B731" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C731" s="32" t="inlineStr">
@@ -35260,7 +35260,7 @@
     <row r="732">
       <c r="B732" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C732" s="32" t="inlineStr">
@@ -35284,7 +35284,7 @@
     <row r="733">
       <c r="B733" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C733" s="32" t="inlineStr">
@@ -35308,7 +35308,7 @@
     <row r="734">
       <c r="B734" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C734" s="32" t="inlineStr">
@@ -35332,7 +35332,7 @@
     <row r="735">
       <c r="B735" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C735" s="32" t="inlineStr">
@@ -35356,7 +35356,7 @@
     <row r="736">
       <c r="B736" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C736" s="32" t="inlineStr">
@@ -35380,7 +35380,7 @@
     <row r="737">
       <c r="B737" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C737" s="32" t="inlineStr">
@@ -35404,7 +35404,7 @@
     <row r="738">
       <c r="B738" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C738" s="32" t="inlineStr">
@@ -35428,7 +35428,7 @@
     <row r="739">
       <c r="B739" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C739" s="32" t="inlineStr">
@@ -35452,7 +35452,7 @@
     <row r="740">
       <c r="B740" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C740" s="32" t="inlineStr">
@@ -35476,7 +35476,7 @@
     <row r="741">
       <c r="B741" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C741" s="32" t="inlineStr">
@@ -35500,7 +35500,7 @@
     <row r="742">
       <c r="B742" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C742" s="32" t="inlineStr">
@@ -35524,7 +35524,7 @@
     <row r="743">
       <c r="B743" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C743" s="32" t="inlineStr">
@@ -35548,7 +35548,7 @@
     <row r="744">
       <c r="B744" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C744" s="32" t="inlineStr">
@@ -35572,7 +35572,7 @@
     <row r="745">
       <c r="B745" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C745" s="32" t="inlineStr">
@@ -35596,7 +35596,7 @@
     <row r="746">
       <c r="B746" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C746" s="32" t="inlineStr">
@@ -35620,7 +35620,7 @@
     <row r="747">
       <c r="B747" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C747" s="32" t="inlineStr">
@@ -35644,7 +35644,7 @@
     <row r="748">
       <c r="B748" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C748" s="32" t="inlineStr">
@@ -35668,7 +35668,7 @@
     <row r="749">
       <c r="B749" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C749" s="32" t="inlineStr">
@@ -35692,7 +35692,7 @@
     <row r="750">
       <c r="B750" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C750" s="32" t="inlineStr">
@@ -35716,7 +35716,7 @@
     <row r="751">
       <c r="B751" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C751" s="32" t="inlineStr">
@@ -35740,7 +35740,7 @@
     <row r="752">
       <c r="B752" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C752" s="32" t="inlineStr">
@@ -35764,7 +35764,7 @@
     <row r="753">
       <c r="B753" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C753" s="32" t="inlineStr">
@@ -35788,7 +35788,7 @@
     <row r="754">
       <c r="B754" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C754" s="32" t="inlineStr">

--- a/docs/data/july_pickup.xlsx
+++ b/docs/data/july_pickup.xlsx
@@ -710,7 +710,7 @@
     </row>
     <row r="3">
       <c r="L3" s="2" t="n">
-        <v>46297</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="4">
@@ -2545,7 +2545,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>10/01 (목)</t>
+          <t>10/05 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -2786,7 +2786,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/04 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -3027,7 +3027,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>10/03 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -3268,7 +3268,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>10/02 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -3509,7 +3509,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -3750,7 +3750,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -3991,7 +3991,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -4232,7 +4232,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -4473,7 +4473,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -4714,7 +4714,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -4955,7 +4955,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -5196,7 +5196,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -5437,7 +5437,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -5678,7 +5678,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -5919,7 +5919,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -6160,7 +6160,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -6401,7 +6401,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -6642,7 +6642,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -6883,7 +6883,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -7124,7 +7124,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -7365,7 +7365,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -7606,7 +7606,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -7847,7 +7847,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -8088,7 +8088,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -8329,7 +8329,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -8570,7 +8570,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -8811,7 +8811,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -9052,7 +9052,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -9293,7 +9293,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -9534,7 +9534,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -10490,7 +10490,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>10/01 (목)</t>
+          <t>10/05 (월)</t>
         </is>
       </c>
       <c r="C6" s="26" t="n">
@@ -10731,7 +10731,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/30 (수)</t>
+          <t>10/04 (일)</t>
         </is>
       </c>
       <c r="C7" s="26" t="n">
@@ -10972,7 +10972,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/29 (화)</t>
+          <t>10/03 (토)</t>
         </is>
       </c>
       <c r="C8" s="26" t="n">
@@ -11213,7 +11213,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/28 (월)</t>
+          <t>10/02 (금)</t>
         </is>
       </c>
       <c r="C9" s="26" t="n">
@@ -11454,7 +11454,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/27 (일)</t>
+          <t>10/01 (목)</t>
         </is>
       </c>
       <c r="C10" s="26" t="n">
@@ -11695,7 +11695,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/26 (토)</t>
+          <t>09/30 (수)</t>
         </is>
       </c>
       <c r="C11" s="26" t="n">
@@ -11936,7 +11936,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/25 (금)</t>
+          <t>09/29 (화)</t>
         </is>
       </c>
       <c r="C12" s="26" t="n">
@@ -12177,7 +12177,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/24 (목)</t>
+          <t>09/28 (월)</t>
         </is>
       </c>
       <c r="C13" s="26" t="n">
@@ -12418,7 +12418,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/23 (수)</t>
+          <t>09/27 (일)</t>
         </is>
       </c>
       <c r="C14" s="26" t="n">
@@ -12659,7 +12659,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/22 (화)</t>
+          <t>09/26 (토)</t>
         </is>
       </c>
       <c r="C15" s="26" t="n">
@@ -12900,7 +12900,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/21 (월)</t>
+          <t>09/25 (금)</t>
         </is>
       </c>
       <c r="C16" s="26" t="n">
@@ -13141,7 +13141,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/20 (일)</t>
+          <t>09/24 (목)</t>
         </is>
       </c>
       <c r="C17" s="26" t="n">
@@ -13382,7 +13382,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/19 (토)</t>
+          <t>09/23 (수)</t>
         </is>
       </c>
       <c r="C18" s="26" t="n">
@@ -13623,7 +13623,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/18 (금)</t>
+          <t>09/22 (화)</t>
         </is>
       </c>
       <c r="C19" s="26" t="n">
@@ -13864,7 +13864,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/17 (목)</t>
+          <t>09/21 (월)</t>
         </is>
       </c>
       <c r="C20" s="26" t="n">
@@ -14105,7 +14105,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/16 (수)</t>
+          <t>09/20 (일)</t>
         </is>
       </c>
       <c r="C21" s="26" t="n">
@@ -14346,7 +14346,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/15 (화)</t>
+          <t>09/19 (토)</t>
         </is>
       </c>
       <c r="C22" s="26" t="n">
@@ -14587,7 +14587,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/14 (월)</t>
+          <t>09/18 (금)</t>
         </is>
       </c>
       <c r="C23" s="26" t="n">
@@ -14828,7 +14828,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/13 (일)</t>
+          <t>09/17 (목)</t>
         </is>
       </c>
       <c r="C24" s="26" t="n">
@@ -15069,7 +15069,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/12 (토)</t>
+          <t>09/16 (수)</t>
         </is>
       </c>
       <c r="C25" s="26" t="n">
@@ -15310,7 +15310,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/11 (금)</t>
+          <t>09/15 (화)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
@@ -15551,7 +15551,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/10 (목)</t>
+          <t>09/14 (월)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
@@ -15792,7 +15792,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/09 (수)</t>
+          <t>09/13 (일)</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
@@ -16033,7 +16033,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/08 (화)</t>
+          <t>09/12 (토)</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
@@ -16274,7 +16274,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/07 (월)</t>
+          <t>09/11 (금)</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
@@ -16515,7 +16515,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/06 (일)</t>
+          <t>09/10 (목)</t>
         </is>
       </c>
       <c r="C31" s="26" t="n">
@@ -16756,7 +16756,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C32" s="26" t="n">
@@ -16997,7 +16997,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C33" s="26" t="n">
@@ -17238,7 +17238,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C34" s="26" t="n">
@@ -17479,7 +17479,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C35" s="26" t="n">
@@ -17812,7 +17812,7 @@
     <row r="5">
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="6">
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -17860,7 +17860,7 @@
     <row r="7">
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -17884,7 +17884,7 @@
     <row r="8">
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -17908,7 +17908,7 @@
     <row r="9">
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -17932,7 +17932,7 @@
     <row r="10">
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C10" s="32" t="inlineStr">
@@ -17956,7 +17956,7 @@
     <row r="11">
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C11" s="32" t="inlineStr">
@@ -17980,7 +17980,7 @@
     <row r="12">
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
@@ -18028,7 +18028,7 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C14" s="32" t="inlineStr">
@@ -18052,7 +18052,7 @@
     <row r="15">
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
@@ -18076,7 +18076,7 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -18100,7 +18100,7 @@
     <row r="17">
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -18124,7 +18124,7 @@
     <row r="18">
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="19">
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -18172,7 +18172,7 @@
     <row r="20">
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
@@ -18196,7 +18196,7 @@
     <row r="21">
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
@@ -18220,7 +18220,7 @@
     <row r="22">
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C22" s="32" t="inlineStr">
@@ -18244,7 +18244,7 @@
     <row r="23">
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -18268,7 +18268,7 @@
     <row r="24">
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C24" s="32" t="inlineStr">
@@ -18292,7 +18292,7 @@
     <row r="25">
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
@@ -18316,7 +18316,7 @@
     <row r="26">
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
@@ -18340,7 +18340,7 @@
     <row r="27">
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C27" s="32" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="28">
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -18388,7 +18388,7 @@
     <row r="29">
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>09/02 (수)</t>
+          <t>09/06 (일)</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="30">
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -18436,7 +18436,7 @@
     <row r="31">
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr">
@@ -18460,7 +18460,7 @@
     <row r="32">
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr">
@@ -18484,7 +18484,7 @@
     <row r="33">
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
@@ -18508,7 +18508,7 @@
     <row r="34">
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -18532,7 +18532,7 @@
     <row r="35">
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C35" s="32" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="36">
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
@@ -18580,7 +18580,7 @@
     <row r="37">
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
@@ -18604,7 +18604,7 @@
     <row r="38">
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C38" s="32" t="inlineStr">
@@ -18628,7 +18628,7 @@
     <row r="39">
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C39" s="32" t="inlineStr">
@@ -18652,7 +18652,7 @@
     <row r="40">
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr">
@@ -18676,7 +18676,7 @@
     <row r="41">
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr">
@@ -18700,7 +18700,7 @@
     <row r="42">
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
@@ -18724,7 +18724,7 @@
     <row r="43">
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -18748,7 +18748,7 @@
     <row r="44">
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
@@ -18772,7 +18772,7 @@
     <row r="45">
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
@@ -18796,7 +18796,7 @@
     <row r="46">
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
@@ -18820,7 +18820,7 @@
     <row r="47">
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
@@ -18844,7 +18844,7 @@
     <row r="48">
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
@@ -18868,7 +18868,7 @@
     <row r="49">
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
@@ -18892,7 +18892,7 @@
     <row r="50">
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
@@ -18916,7 +18916,7 @@
     <row r="51">
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
@@ -18940,7 +18940,7 @@
     <row r="52">
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="53">
       <c r="B53" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -18988,7 +18988,7 @@
     <row r="54">
       <c r="B54" s="25" t="inlineStr">
         <is>
-          <t>09/03 (목)</t>
+          <t>09/07 (월)</t>
         </is>
       </c>
       <c r="C54" s="32" t="inlineStr">
@@ -19012,7 +19012,7 @@
     <row r="55">
       <c r="B55" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
@@ -19036,7 +19036,7 @@
     <row r="56">
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
@@ -19060,7 +19060,7 @@
     <row r="57">
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
@@ -19084,7 +19084,7 @@
     <row r="58">
       <c r="B58" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
@@ -19108,7 +19108,7 @@
     <row r="59">
       <c r="B59" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -19132,7 +19132,7 @@
     <row r="60">
       <c r="B60" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
@@ -19156,7 +19156,7 @@
     <row r="61">
       <c r="B61" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
@@ -19180,7 +19180,7 @@
     <row r="62">
       <c r="B62" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
@@ -19204,7 +19204,7 @@
     <row r="63">
       <c r="B63" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
@@ -19228,7 +19228,7 @@
     <row r="64">
       <c r="B64" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
@@ -19252,7 +19252,7 @@
     <row r="65">
       <c r="B65" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
@@ -19276,7 +19276,7 @@
     <row r="66">
       <c r="B66" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
@@ -19300,7 +19300,7 @@
     <row r="67">
       <c r="B67" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
@@ -19324,7 +19324,7 @@
     <row r="68">
       <c r="B68" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr">
@@ -19348,7 +19348,7 @@
     <row r="69">
       <c r="B69" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="70">
       <c r="B70" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
@@ -19396,7 +19396,7 @@
     <row r="71">
       <c r="B71" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
@@ -19420,7 +19420,7 @@
     <row r="72">
       <c r="B72" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
@@ -19444,7 +19444,7 @@
     <row r="73">
       <c r="B73" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C73" s="32" t="inlineStr">
@@ -19468,7 +19468,7 @@
     <row r="74">
       <c r="B74" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr">
@@ -19492,7 +19492,7 @@
     <row r="75">
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C75" s="32" t="inlineStr">
@@ -19516,7 +19516,7 @@
     <row r="76">
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C76" s="32" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="77">
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C77" s="32" t="inlineStr">
@@ -19564,7 +19564,7 @@
     <row r="78">
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
@@ -19588,7 +19588,7 @@
     <row r="79">
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>09/04 (금)</t>
+          <t>09/08 (화)</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
@@ -19612,7 +19612,7 @@
     <row r="80">
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
@@ -19636,7 +19636,7 @@
     <row r="81">
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
@@ -19660,7 +19660,7 @@
     <row r="82">
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
@@ -19684,7 +19684,7 @@
     <row r="83">
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C83" s="32" t="inlineStr">
@@ -19708,7 +19708,7 @@
     <row r="84">
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C84" s="32" t="inlineStr">
@@ -19732,7 +19732,7 @@
     <row r="85">
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C85" s="32" t="inlineStr">
@@ -19756,7 +19756,7 @@
     <row r="86">
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
@@ -19780,7 +19780,7 @@
     <row r="87">
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>09/05 (토)</t>
+          <t>09/09 (수)</t>
         </is>
       